--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N127_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N127_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.59285849646431</v>
+        <v>7.08383950567545</v>
       </c>
       <c r="D2" t="n">
-        <v>44.00978356430461</v>
+        <v>7.1515898291995</v>
       </c>
       <c r="E2" t="n">
-        <v>12.04760482639249</v>
+        <v>1.957735784288779</v>
       </c>
       <c r="F2" t="n">
-        <v>12.65246260063553</v>
+        <v>2.056025172603273</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49764884367934</v>
+        <v>3.168367937097892</v>
       </c>
       <c r="D3" t="n">
-        <v>18.70485836303356</v>
+        <v>3.039539483992954</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04760482639249</v>
+        <v>1.957735784288779</v>
       </c>
       <c r="F3" t="n">
-        <v>12.65246260063553</v>
+        <v>2.056025172603273</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
